--- a/processed_ruby_restored_xlsx/sc243_みるく５：ソープごっこ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc243_みるく５：ソープごっこ.ss.xlsx
@@ -776,8 +776,8 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>「Um~ let's see… a florist or a sweet shop！ And then, a
-clerk at a fancy goods shop！」</t>
+          <t>「Um~ let's see… a florist or a sweet shop！ And then,
+a clerk at a fancy goods shop！」</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -898,8 +898,8 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>「Alright, I'll get the ingredients ready, so how about
-we try a bakery job experience next time？」</t>
+          <t>「Alright, I'll get the ingredients ready, so how
+about we try a bakery job experience next time？」</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -975,8 +975,8 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>「Oh, you want to go to the place they're showing on TV
-right now？」</t>
+          <t>「Oh, you want to go to the place they're showing on
+TV right now？」</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1097,8 +1097,8 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>But if I leave Makishima by ferry and then... it takes
-time to get anywhere.</t>
+          <t>But if I leave Makishima by ferry and then... it
+takes time to get anywhere.</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1268,8 +1268,9 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>In that case, maybe I'll get everyone on the island to
-help and line up places to sell the sweets we make...</t>
+          <t>In that case, maybe I'll get everyone on the island
+to help and line up places to sell the sweets we
+make...</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1406,9 +1407,9 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>Even without going into details, Miru-chan is just the
-type who pulls back a bit and then goes along when you
-push her.</t>
+          <t>Even without going into details, Miru-chan is just
+the type who pulls back a bit and then goes along
+when you push her.</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1816,8 +1817,8 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>「Today’s job I want Miru-chan to try is… guess what, a
-soap lady！」</t>
+          <t>「Today’s job I want Miru-chan to try is… guess what,
+a soap lady！」</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2257,8 +2258,8 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ B-because... doing it naked is... an erotic job,
-isn't it？」</t>
+          <t>「Huh？ B-because... doing it naked is... an erotic
+job, isn't it？」</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3374,8 +3375,8 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>「Okay, then... could you spread that more and cling to
-my back to wash me？」</t>
+          <t>「Okay, then... could you spread that more and cling
+to my back to wash me？」</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -4032,8 +4033,8 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>The lotion and Miru-chan's skin against my heated body
-made me feel even hotter...</t>
+          <t>The lotion and Miru-chan's skin against my heated
+body made me feel even hotter...</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4063,7 +4064,8 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>「Alright... shall we try it from the front this time？」</t>
+          <t>「Alright... shall we try it from the front this
+time？」</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4368,8 +4370,8 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>...Before I knew it, the two of us had already reached
-our peak.</t>
+          <t>...Before I knew it, the two of us had already
+reached our peak.</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4688,7 +4690,8 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>「Mmm… then, Onii-chan… I'm going to put it in, okay…？」</t>
+          <t>「Mmm… then, Onii-chan… I'm going to put it in,
+okay…？」</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4795,7 +4798,8 @@
       <c r="B284" s="1" t="inlineStr">
         <is>
           <t>When Miru-chan drops her hips, my penis is swallowed
-in all at once, and Miru-chan lets out a startled cry.</t>
+in all at once, and Miru-chan lets out a startled
+cry.</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4977,8 +4981,8 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>I let out a relieved breath, but Miru-chan's breathing
-only grows more ragged.</t>
+          <t>I let out a relieved breath, but Miru-chan's
+breathing only grows more ragged.</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -5038,8 +5042,8 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>「I'm okay, buuut... heh, it's a weird feeling...！ It's
-kind of slipping...」</t>
+          <t>「I'm okay, buuut... heh, it's a weird feeling...！
+It's kind of slipping...」</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5115,8 +5119,8 @@
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>When I gently reach out my hand, Miru-chan reaches out
-and grabs it in return.</t>
+          <t>When I gently reach out my hand, Miru-chan reaches
+out and grabs it in return.</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5497,8 +5501,8 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>「Today is Miru-chan's work experience... so I want you
-to make me feel good.」</t>
+          <t>「Today is Miru-chan's work experience... so I want
+you to make me feel good.」</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5667,8 +5671,8 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>And because she squeezes so tightly, my penis is being
-pulled and tugged hard.</t>
+          <t>And because she squeezes so tightly, my penis is
+being pulled and tugged hard.</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -5850,8 +5854,8 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t>...Once more—this time lifting her hips just a little,
-and then dropping back down.</t>
+          <t>...Once more—this time lifting her hips just a
+little, and then dropping back down.</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -6142,7 +6146,8 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>Even so, her saying she wants more is just so cute...！</t>
+          <t>Even so, her saying she wants more is just so
+cute...！</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6691,8 +6696,8 @@
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t>Like she's been melted by pleasure—a little loose, but
-the face I love.</t>
+          <t>Like she's been melted by pleasure—a little loose,
+but the face I love.</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -6722,8 +6727,8 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nnn... Onii-chan's face... I'm gonna make it even
-weirder！」</t>
+          <t>「Nn, nnn... Onii-chan's face... I'm gonna make it
+even weirder！」</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -6768,8 +6773,8 @@
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan watches my face intently and laughs, clearly
-enjoying herself.</t>
+          <t>Miru-chan watches my face intently and laughs,
+clearly enjoying herself.</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -6953,8 +6958,8 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t>「Hehe... Miru-chan's body is really... so naughty, you
-know？」</t>
+          <t>「Hehe... Miru-chan's body is really... so naughty,
+you know？」</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -7121,8 +7126,8 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t>Being rubbed back and forth against my hips, the penis
-starts trembling inside her pussy.</t>
+          <t>Being rubbed back and forth against my hips, the
+penis starts trembling inside her pussy.</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -7650,8 +7655,8 @@
       </c>
       <c r="B470" s="1" t="inlineStr">
         <is>
-          <t>...Miru-chan's hips began trembling violently, and her
-voice shook with them.</t>
+          <t>...Miru-chan's hips began trembling violently, and
+her voice shook with them.</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -8019,8 +8024,8 @@
       </c>
       <c r="B494" s="1" t="inlineStr">
         <is>
-          <t>When Miru-chan starts repeating “penis” over and over,
-my own level of arousal rises even more.</t>
+          <t>When Miru-chan starts repeating “penis” over and
+over, my own level of arousal rises even more.</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -8177,8 +8182,8 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>「Hah, haha！ Miru-chan’s body… it’s gone all melted and
-sloppy now…」</t>
+          <t>「Hah, haha！ Miru-chan’s body… it’s gone all melted
+and sloppy now…」</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -8315,8 +8320,8 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>There was nothing but pleasure, over and over until it
-swallowed everything.</t>
+          <t>There was nothing but pleasure, over and over until
+it swallowed everything.</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -8557,8 +8562,8 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>「Fuuwaaa！ Onii-chan！ Together！ Together is… good, it’s
-good！」</t>
+          <t>「Fuuwaaa！ Onii-chan！ Together！ Together is… good,
+it’s good！」</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -8603,8 +8608,8 @@
       </c>
       <c r="B532" s="1" t="inlineStr">
         <is>
-          <t>Her pussy kept throbbing, sending out signals that she
-was at her limit.</t>
+          <t>Her pussy kept throbbing, sending out signals that
+she was at her limit.</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -8650,8 +8655,8 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>「Aahhh！ Oniichan！ Ha, haaah！ Miru... I'm cumming！ It's
-amazing, aaahhh！」</t>
+          <t>「Aahhh！ Oniichan！ Ha, haaah！ Miru... I'm cumming！
+It's amazing, aaahhh！」</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -9050,8 +9055,8 @@
       </c>
       <c r="B561" s="1" t="inlineStr">
         <is>
-          <t>Still drenched in that overly erotic sensation, I look
-up at Miru-chan's face.</t>
+          <t>Still drenched in that overly erotic sensation, I
+look up at Miru-chan's face.</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -9249,8 +9254,8 @@
       </c>
       <c r="B574" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, slick with lotion and sweat, is bouncing on
-top of me… this is so hot！</t>
+          <t>Miru-chan, slick with lotion and sweat, is bouncing
+on top of me… this is so hot！</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -9587,8 +9592,8 @@
       </c>
       <c r="B596" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, bathed in semen falling onto her body, lets
-an entranced expression cross her face.</t>
+          <t>Miru-chan, bathed in semen falling onto her body,
+lets an entranced expression cross her face.</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -9694,8 +9699,8 @@
       </c>
       <c r="B603" s="1" t="inlineStr">
         <is>
-          <t>...But when I stop ejaculating, Miru-chan mutters that
-sadly.</t>
+          <t>...But when I stop ejaculating, Miru-chan mutters
+that sadly.</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -9710,8 +9715,8 @@
       </c>
       <c r="B604" s="1" t="inlineStr">
         <is>
-          <t>Because she's so innocent, does she think internal cum
-is the obvious thing to do？</t>
+          <t>Because she's so innocent, does she think internal
+cum is the obvious thing to do？</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -9803,8 +9808,8 @@
       </c>
       <c r="B610" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ Ahaha, ahaha...！ It's because Miru-chan tried so
-hard for me！」</t>
+          <t>「Huh？ Ahaha, ahaha...！ It's because Miru-chan tried
+so hard for me！」</t>
         </is>
       </c>
       <c r="C610" t="n">

--- a/processed_ruby_restored_xlsx/sc243_みるく５：ソープごっこ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc243_みるく５：ソープごっこ.ss.xlsx
@@ -898,8 +898,8 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>「Alright, I'll get the ingredients ready, so how
-about we try a bakery job experience next time？」</t>
+          <t>Alright, I」ll get the ingredients ready, so how about
+we try a bakery job experience next time？</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -975,8 +975,8 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>「Oh, you want to go to the place they're showing on
-TV right now？」</t>
+          <t>Oh, you want to go to the place they're showing on TV
+right now？</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru-chan</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>When I immediately refused, Miru-chan puffed her
+          <t>When he immediately refused, Miru-chan puffed her
 cheeks out.</t>
         </is>
       </c>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>「Yeah！ I'm gonna do it—！」</t>
+          <t>Yeah！ I」m gonna do it—！</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>「Oh！ Ohhh~！ Did the hot water get all gooey！？」</t>
+          <t>Oh！ Ohhh~！ Did the hot water get all gooey！？</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>I hold out a bucket full of lotion, and Miru-chan
+          <t>He holds out a bucket full of lotion, and Miru-chan
 eagerly sticks her hand in, looking excited.</t>
         </is>
       </c>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>「O-Onii-chan？ What are you doing！？」</t>
+          <t>O-Onii-chan？ What are you doing！？</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3039,8 +3039,8 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>「You rub this all over your body and wash with it,
-okay？」</t>
+          <t>You rub this all over your body and wash with it,
+okay？</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>「F... feh？ But it's all slippery... it feels...」</t>
+          <t>F... feh？ But it's all slippery... it feels...</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>「Feels good, doesn't it？ This texture...」</t>
+          <t>Feels good, doesn't it？ This texture...</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>「Uh... umm...」</t>
+          <t>Uh... umm...</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>「Here, try doing it yourself, okay？」</t>
+          <t>Here, try doing it yourself, okay？</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3267,9 +3267,9 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>Even though she's doing it hesitantly, the little
-moans slipping out that sound like she's enjoying it
-are so cute…！</t>
+          <t>Even though they're doing it hesitantly, the little
+moans slipping out that sound like they're enjoying
+it are so cute…！</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>「Onii-chan... gyuuu...！」</t>
+          <t>Onii-chan... gyuuu...！</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>「...!　Miru-chan...!」</t>
+          <t>...!　Miru-chan...!</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4247,8 +4247,8 @@
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>When Miru-chan suddenly threw her arms around me, I
-caught her and my heart started pounding hard.</t>
+          <t>When Miru-chan suddenly threw her arms around him, he
+caught her and his heart started pounding hard.</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4263,8 +4263,8 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>Even stronger than that, down below my penis throbbed
-violently.</t>
+          <t>Even stronger than that, down below his penis
+throbbed violently.</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>「Ah... your penis... it's getting so big...」</t>
+          <t>Ah... your penis... it's getting so big...</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4324,8 +4324,8 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>「It's because of you, Miru-chan... it feels really
-good...」</t>
+          <t>It's because of you, Miru-chan... it feels really
+good...</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t>「Nn...？ Eh... eeh...？」</t>
+          <t>Nn...？ Eh... eeh...？</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>「...Is that... part of your job too？」</t>
+          <t>...Is that... part of your job too？</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4570,7 +4570,7 @@
       <c r="B269" s="1" t="inlineStr">
         <is>
           <t>I could even feel lotion dripping from my fingers and
-wetting my penis...！</t>
+wetting his penis...！</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnuu...！」</t>
+          <t>Nn... nnuu...！</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>「A-are you okay？ Does it... hurt？」</t>
+          <t>A-are you okay？ Does it... hurt？</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>「I-it hurts... haah, fuu！ I don't... think so？」</t>
+          <t>I-it hurts... haah, fuu！ I don't... think so？</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan's fingers tense, and my gaze drops to the
+          <t>Miru-chan's fingers tense, and his gaze drops to the
 spot where their eyes are quietly connected.</t>
         </is>
       </c>
@@ -5563,8 +5563,8 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>And slowly, as if checking the sensation, she lifts
-her hips.</t>
+          <t>And slowly, as if checking the sensation, they lift
+their hips.</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>「B-but, b-but... just one more time... ahh！」</t>
+          <t>B-but, b-but... just one more time... ahh！</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5885,8 +5885,7 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>「Fuhaa！ That feels great. Keep going like that...
-ffu！」</t>
+          <t>Fuhaa！ That feels great. Keep going like that... ffu！</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -7051,7 +7050,7 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t>「Onii-chan... auh！ More, more！」</t>
+          <t>Onii-chan... auh！ More, more！</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -7111,7 +7110,7 @@
       </c>
       <c r="B435" s="1" t="inlineStr">
         <is>
-          <t>「Nnffah！ It's all squelchy… Nn！ I like this…！」</t>
+          <t>Nnffah！ It」s all squelchy… Nn！ I like this…！</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -7126,7 +7125,7 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t>Being rubbed back and forth against my hips, the
+          <t>Being rubbed back and forth against his hips, the
 penis starts trembling inside her pussy.</t>
         </is>
       </c>
@@ -7174,8 +7173,8 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>「Uhhah！ Nnngh, nn~！ In there... deep inside... Ah,
-hah！ It's hitting... oooaaahhh~ ah！」</t>
+          <t>Uhhah！ Nnngh, nn~！ In there... deep inside... Ah,
+hah！ It's hitting... oooaaahhh~ ah！</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7978,7 +7977,7 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>「Heh-heh... ah ha！ I wonder what's come to me？」</t>
+          <t>Heh-heh... ah ha！ I wonder what」s come to me？</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -8072,8 +8071,8 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>「Fuhaah！ Auuuu… it's hot… but it feels so good！
-Onii-chan！ Nn！ Nnnh！」</t>
+          <t>Fuhaah！ Auuuu… it」s hot… but it feels so good！
+Onii-chan！ Nn！ Nnnh！</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8104,8 +8103,8 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>As if her body is rejoicing along with the feelings,
-she bounces up and down on top of me.</t>
+          <t>As if their body is rejoicing along with the
+feelings, they bounce up and down on top of me.</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8456,7 +8455,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>My penis heated and melted, swelling even bigger.</t>
+          <t>His penis heated and melted, swelling even bigger.</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8624,7 +8623,7 @@
       </c>
       <c r="B533" s="1" t="inlineStr">
         <is>
-          <t>My penis was being rubbed in short, shaking strokes,
+          <t>His penis was being rubbed in short, shaking strokes,
 and a powerful orgasm was rising up...！</t>
         </is>
       </c>
@@ -8780,7 +8779,7 @@
       <c r="B543" s="1" t="inlineStr">
         <is>
           <t>Semen and lube mix together, heating her pussy along
-with my penis until it feels like it’s melting...</t>
+with his penis until it feels like it’s melting...</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -9209,7 +9208,7 @@
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
-          <t>「Nn！　Fuuuh！　Nn！　Nnnh！」</t>
+          <t>Nn！　Fuuuh！　Nn！　Nnnh！</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -9301,7 +9300,7 @@
       </c>
       <c r="B577" s="1" t="inlineStr">
         <is>
-          <t>「Nnnh！ Onii-chan！ Ha—, Fwaaah！ Ahn！ Aah...！」</t>
+          <t>Nnnh！ Onii-chan！ Ha—, Fwaaah！ Ahn！ Aah...！</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -9454,7 +9453,7 @@
       </c>
       <c r="B587" s="1" t="inlineStr">
         <is>
-          <t>「Uahh...！？ Fuwaah... Ah, ah, fuwaa... Nn, nnn...！」</t>
+          <t>Uahh...！？ Fuwaah... Ah, ah, fuwaa... Nn, nnn...！</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -9699,7 +9698,7 @@
       </c>
       <c r="B603" s="1" t="inlineStr">
         <is>
-          <t>...But when I stop ejaculating, Miru-chan mutters
+          <t>...But when he stops ejaculating, Miru-chan mutters
 that sadly.</t>
         </is>
       </c>
